--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_198_Cyprus_South.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_198_Cyprus_South.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R77fe910163334bed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R00a10d03e5204288"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rfde27a3c4bf24242"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rf012c45ebaf44e86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rea4fe146329540a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R95f23b5a9230436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb64002f7bc334e77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R6b740b53ec604589"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R93f3044869ef499c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R02592c56984f42c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R5f88f5d40d914dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R75076be65a8f48f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ198CommercialTable" displayName="EEZ198CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ198CommercialTable" displayName="EEZ198CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ198FunctionalTable" displayName="EEZ198FunctionalTable" ref="A1:O22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O22"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ198FunctionalTable" displayName="EEZ198FunctionalTable" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E22"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ198ValidationTable" displayName="EEZ198ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ198ValidationTable" displayName="EEZ198ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6724,7 +6678,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2696db14186a4938"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7fbfcc287c94661"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6734,20 +6688,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6755,606 +6699,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.18474450209999999</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.18474450209999999</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$91,A2,'Species'!$U$2:$U$91))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>23.79970220080962</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>23.79970220080962</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>13.650335744</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.0764897717847672</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>119.2586178527368</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>13.650335744</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>145.12819113873178</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$91,A3,'Species'!$U$2:$U$91))</x:f>
-        <x:v>1981.0485349630944</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.0764897717847672</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>119.2586178527368</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1627.9201740552496</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>353.1283609078448</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2169199488622222</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.21691994886222232</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1.077885798</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.539651668831061</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>346.45885744507626</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1.077885798</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>354.89556611076415</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$91,A4,'Species'!$U$2:$U$91))</x:f>
-        <x:v>382.5368904839628</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.539651668831061</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>346.45885744507626</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>373.44308203135427</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>9.093808452608528</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0243512569657</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.024351256965700094</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.4673147882</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.4673147882</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$91,A5,'Species'!$U$2:$U$91))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>67.54753803219899</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>67.54753803219899</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>9.9832795396</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.7687499631922057</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>58.71512140296415</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>9.9832795396</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>109.89022349610913</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$91,A6,'Species'!$U$2:$U$91))</x:f>
-        <x:v>1097.0648198307774</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.7687499631922057</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>58.71512140296415</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>586.1694701673421</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>510.89534966343535</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.8715830074152153</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.8715830074152153</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>719.0743559684001</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4599383005216233</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>288.362180277965</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>719.0743559684001</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>347.4292464191512</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$91,A7,'Species'!$U$2:$U$91))</x:f>
-        <x:v>249827.4616134377</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4599383005216233</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>288.362180277965</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>207353.8490690214</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>42473.612544416304</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2048363834822193</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.20483638348221936</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>758.8191626294</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.385985719270885</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>243.21240332118285</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>758.8191626294</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>575.6654867066858</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$91,A8,'Species'!$U$2:$U$91))</x:f>
-        <x:v>436826.0025774133</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.385985719270885</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>243.21240332118285</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>184554.23222926387</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>252271.7703481494</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>2.366924872439462</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>1.3669248724394623</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>20.1434932779</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8392390105814562</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>690.6197764816461</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>20.1434932779</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>695.9331991261172</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$91,A9,'Species'!$U$2:$U$91))</x:f>
-        <x:v>14018.525718464383</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8392390105814562</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>690.6197764816461</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>13911.494825142838</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>107.03089332154559</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0076937018391514</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.007693701839151325</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>32.3608653682</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7318388068936335</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>539.3104144542236</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>32.3608653682</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>774.116025779808</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$91,A10,'Species'!$U$2:$U$91))</x:f>
-        <x:v>25051.06448962641</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7318388068936335</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>539.3104144542236</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>17452.551713821274</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>7598.512775805135</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.4353811924125464</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.4353811924125463</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>680.4472126390999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.3172602012408055</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2076.157044282365</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>680.4472126390999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2096.3456503511106</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$91,A11,'Species'!$U$2:$U$91))</x:f>
-        <x:v>1426452.5545095142</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.3172602012408055</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2076.157044282365</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1412715.2737829676</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>13737.280726546654</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0097240264768717</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.009724026476871718</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbfcbbf40c2c4872"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R908e4ec12a9c4c74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7364,20 +6914,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7385,1200 +6925,421 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>35.3062523158</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.076541890861427</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1192.729307723935</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>35.3062523158</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1427.5848082044342</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$91,A2,'Species'!$U$2:$U$91))</x:f>
-        <x:v>50402.66944066871</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.076541890861427</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1192.729307723935</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>42110.80188295072</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>8291.86755771799</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.196905952557391</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.19690595255739107</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.0208890195</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.14</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1380.3842646028838</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.0208890195</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1380.3842646028838</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$91,A3,'Species'!$U$2:$U$91))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>28.834873820782803</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.14</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1380.3842646028838</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>28.834873820782803</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>5.5405217336</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.378089809830396</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2388.3051208739616</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>5.5405217336</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2574.688918859555</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$91,A4,'Species'!$U$2:$U$91))</x:f>
-        <x:v>14265.119912200453</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.378089809830396</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2388.3051208739616</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>13232.45642867036</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1032.663483530092</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0780401952650795</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.07804019526507953</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>33.4456937067</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.078579243001814</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1198.3377564495459</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>33.4456937067</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1247.2761615049073</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$91,A5,'Species'!$U$2:$U$91))</x:f>
-        <x:v>41716.01646536161</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.078579243001814</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1198.3377564495459</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>40079.23755938557</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1636.7789059760398</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0408385739262334</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.04083857392623345</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>675.1277131304</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.3075283782863085</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2030.1511725443856</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>675.1277131304</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2061.9421591617684</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$91,A6,'Species'!$U$2:$U$91))</x:f>
-        <x:v>1392074.294522044</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.3075283782863085</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2030.1511725443856</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1370611.3184288912</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>21462.97609315277</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0156594183956946</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.015659418395694718</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>25.1191184184</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6066413443033016</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>404.24191658362923</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>25.1191184184</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>456.6400634389172</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$91,A7,'Species'!$U$2:$U$91))</x:f>
-        <x:v>11470.395828107849</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6066413443033016</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>404.24191658362923</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>10154.200572345157</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1316.1952557626919</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1296207659465909</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.129620765946591</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>506.51184040629994</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.621164480669976</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>417.9886418200083</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>506.51184040629994</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>623.1180887068572</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$91,A8,'Species'!$U$2:$U$91))</x:f>
-        <x:v>315616.6899013663</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.621164480669976</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>417.9886418200083</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>211716.1962371821</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>103900.4936641842</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4907536386483453</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.4907536386483452</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>7.2417469498</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.1661055536178635</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1465.9040800600524</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>7.2417469498</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1875.330463168645</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$91,A9,'Species'!$U$2:$U$91))</x:f>
-        <x:v>13580.668661518557</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.1661055536178635</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1465.9040800600524</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>10615.70640047426</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2964.9622610442966</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2792995726513157</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.2792995726513156</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4.514581081799999</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.1588614078795216</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>144.16552168797023</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4.514581081799999</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>168.361563021726</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$91,A10,'Species'!$U$2:$U$91))</x:f>
-        <x:v>760.0819273201625</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.1588614078795216</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>144.16552168797023</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>650.8469368603379</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>109.23499045982464</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1678351456746041</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.16783514567460406</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>87.37171706250001</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3659917548231477</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>232.26926991035845</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>87.37171706250001</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>262.19699380611206</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$91,A11,'Species'!$U$2:$U$91))</x:f>
-        <x:v>22908.60155746569</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3659917548231477</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>232.26926991035845</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>20293.764932921284</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2614.836624544405</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1288492614942298</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.1288492614942298</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>107.45847268340002</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.5217499241257686</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>332.4680560833266</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>107.45847268340002</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>425.10472246026484</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$91,A12,'Species'!$U$2:$U$91))</x:f>
-        <x:v>45681.104206080716</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.5217499241257686</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>332.4680560833266</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>35726.50952273326</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>9954.594683347459</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2786332842567008</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.2786332842567007</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>454.69362017759994</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.1969944428825583</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>157.39627243262157</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>454.69362017759994</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>185.9903865581374</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$91,A13,'Species'!$U$2:$U$91))</x:f>
-        <x:v>84568.64218235071</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.1969944428825583</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>157.39627243262157</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>71567.08091484848</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>13001.561267502228</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.1816695763094163</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.18166957630941616</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>32.9574581615</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.265911831174911</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1844.6408891380797</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>32.9574581615</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>2360.245561342012</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$91,A14,'Species'!$U$2:$U$91))</x:f>
-        <x:v>77787.69433879544</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.265911831174911</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1844.6408891380797</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>60794.674926760425</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>16993.019412035013</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2795149317354944</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.2795149317354944</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>76.88946265349999</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.9628527714743376</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>91.80213287957677</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>76.88946265349999</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>226.1508099477163</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$91,A15,'Species'!$U$2:$U$91))</x:f>
-        <x:v>17388.614255533706</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.9628527714743376</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>91.80213287957677</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>7058.616667555862</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>10329.997587977845</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>2.4634592122644254</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>1.4634592122644254</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>13.727009665699999</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.6981817873169884</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>49.90933546218537</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>13.727009665699999</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>88.7454428680835</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$91,A16,'Species'!$U$2:$U$91))</x:f>
-        <x:v>1218.2095520370092</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.6981817873169884</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>49.90933546218537</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>685.1059302980823</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>533.1036217389269</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.7781331297292657</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.7781331297292656</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>9.1357546622</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.0357844941431775</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>108.58866506069954</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>9.1357546622</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>133.64704425511664</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$91,A17,'Species'!$U$2:$U$91))</x:f>
-        <x:v>1220.9666076429316</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.0357844941431775</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>108.58866506069954</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>992.0394030903601</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>228.92720455257154</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.2307642255332065</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.23076422553320663</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1.7089417035</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.3832790122287513</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>241.70131443924828</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1.7089417035</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>242.36313999556242</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$91,A18,'Species'!$U$2:$U$91))</x:f>
-        <x:v>414.18447732962545</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.3832790122287513</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>241.70131443924828</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>413.0534560359981</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>1.1310212936273274</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0027381959334793</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0027381959334792675</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>157.5791183422</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.2686998997052963</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>185.6521143641865</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>157.5791183422</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>406.6640817305163</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$91,A19,'Species'!$U$2:$U$91))</x:f>
-        <x:v>64081.76746053511</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.2686998997052963</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>185.6521143641865</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>29254.89649987379</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>34826.87096066133</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>2.190462969534402</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>1.1904629695344018</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>0.6520592903</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.145833765054172</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>139.90517048974817</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>0.6520592903</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>140.09038992601654</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$91,A20,'Species'!$U$2:$U$91))</x:f>
-        <x:v>91.3472402330086</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.145833765054172</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>139.90517048974817</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>91.2264661788457</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0.12077405416290787</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0013238927169024</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.0013238927169023007</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>0.1287932922</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.73</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>537.0317963702527</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>0.1287932922</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$91,A21,'Species'!$U$2:$U$91))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>69.16609307060484</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>69.16609307060484</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>1.077885798</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.539651668831061</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>346.45885744507626</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>1.077885798</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>354.89556611076415</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$91,A22,'Species'!$U$2:$U$91))</x:f>
-        <x:v>382.5368904839628</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.539651668831061</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>346.45885744507626</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>373.44308203135427</x:v>
       </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>9.093808452608528</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0243512569657</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.024351256965700094</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G22">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O22">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72e04e065a79448f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd87d8c17076a4c3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8753,7 +7514,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8852,7 +7613,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>2155727.606393967</x:v>
+        <x:v>1838666.2815867038</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8866,7 +7627,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>2155727.606393967</x:v>
+        <x:v>1926519.177215979</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8880,7 +7641,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-317061.324807263</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8894,7 +7655,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-229208.42917798785</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8905,9 +7666,9 @@
         <x:v>EEZ_198</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8919,47 +7680,19 @@
         <x:v>EEZ_198</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_198</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_198</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c9ad5e1b36945be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b45c9be20c84d6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9006,7 +7739,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
